--- a/InputData/trans/EoFoNVFE/Effect of Feebate on New Veh Fuel Econ.xlsx
+++ b/InputData/trans/EoFoNVFE/Effect of Feebate on New Veh Fuel Econ.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Dropbox (Energy Innovation)\EPS Versions\eps-1.5.0-us-wipL\InputData\trans\EoFoNVFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iamho\Dropbox\Energy Innovation\InputData_RevisionRequest\trans\EoFoNVFE\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D4CC21-B625-4A9E-8630-9FED570EF2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="45" windowWidth="25875" windowHeight="11310"/>
+    <workbookView xWindow="13700" yWindow="730" windowWidth="19800" windowHeight="17010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="Data" sheetId="2" r:id="rId2"/>
-    <sheet name="EoFoNVFE" sheetId="3" r:id="rId3"/>
+    <sheet name="EoFoNVFE" sheetId="3" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>EoFoNVFE Effect of Feebate on New Veh Fuel Economy</t>
   </si>
@@ -29,129 +29,37 @@
     <t>Source:</t>
   </si>
   <si>
-    <t>Feebates, rebates and gas-guzzler taxes: a study of incentives for increased fuel economy.</t>
-  </si>
-  <si>
-    <t>Energy Policy, 33(6), 757-775.</t>
-  </si>
-  <si>
-    <t>http://cta.ornl.gov/cta/Publications/Reports/FeebateEnergyPolicy_FINAL.pdf</t>
-  </si>
-  <si>
-    <t>Greene, D. L., Patterson, P. D., Singh, M., &amp; Li, J.</t>
-  </si>
-  <si>
-    <t>Feebate Amount</t>
-  </si>
-  <si>
-    <t>per Unit</t>
-  </si>
-  <si>
-    <t>Resulting Increase in Fuel Econ</t>
-  </si>
-  <si>
-    <t>percent</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Feebate Rate</t>
-  </si>
-  <si>
-    <t>hundredth gal/mile (0.01 gal/mile)</t>
-  </si>
-  <si>
-    <t>Page 761, Section 3, Paragrah 1 and Page 771, Section A.2, Paragraph 2</t>
-  </si>
-  <si>
     <t>New Vehicle Fuel Econ</t>
-  </si>
-  <si>
-    <t>Note:</t>
-  </si>
-  <si>
-    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
-  </si>
-  <si>
-    <t>We adjust 2000 dollars to 2012 dollars using the following conversion factor:</t>
-  </si>
-  <si>
-    <t>The source specifies that it uses 2000 $, for example, Page 762, Table 1A.</t>
-  </si>
-  <si>
-    <t>2000$</t>
-  </si>
-  <si>
-    <t>perc increase in fuel econ / 2000$</t>
-  </si>
-  <si>
-    <t>perc increase in fuel econ / 2012$</t>
-  </si>
-  <si>
-    <t>Since the feebate is natively expressed in unusual units (dollars per (hundredth gallon per mile)), we</t>
-  </si>
-  <si>
-    <t>cause the lever in the EPS to represent the fraction of the best practice feebate rate, to improve</t>
-  </si>
-  <si>
-    <t>model usability for users.</t>
-  </si>
-  <si>
-    <t>Currency Year</t>
-  </si>
-  <si>
-    <t>Best Practice Feebate Rate</t>
-  </si>
-  <si>
-    <t>2012$ / (hundredth gal/mile)</t>
-  </si>
-  <si>
-    <t>Feebate at Full Policy Implementation</t>
-  </si>
-  <si>
-    <t>perc increase in fuel econ at full policy implementation</t>
-  </si>
-  <si>
-    <t>Effect of Feebate on Fuel Economy</t>
-  </si>
-  <si>
-    <t>Best Practices for Feebate Program Design and Implementation</t>
-  </si>
-  <si>
-    <t>http://www.theicct.org/sites/default/files/publications/ICCT_feebates_may2010.pdf</t>
-  </si>
-  <si>
-    <t>Table 2</t>
-  </si>
-  <si>
-    <t>John German and Dan Meszler, ICCT</t>
-  </si>
-  <si>
-    <t>This rate is from Germany.</t>
-  </si>
-  <si>
-    <t>Notes</t>
   </si>
   <si>
     <t>Effect of Feebate (dimensionless)</t>
   </si>
+  <si>
+    <t>no data</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Notes</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">In South Korea, there is no subsidies or tax benefits for fuel-efficient vehicles. </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>We set all values to be 0.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -159,15 +67,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -175,14 +75,14 @@
       <b/>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -190,23 +90,24 @@
       <b/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -254,64 +155,46 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="8">
+  <cellStyleXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="8">
-    <cellStyle name="Body: normal cell" xfId="5"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="3"/>
-    <cellStyle name="Footnotes: top row" xfId="7"/>
-    <cellStyle name="Header: bottom row" xfId="4"/>
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Parent row" xfId="6"/>
-    <cellStyle name="Table title" xfId="2"/>
+  <cellStyles count="7">
+    <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Header: bottom row" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Table title" xfId="1" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -327,7 +210,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -402,6 +285,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -437,6 +337,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -612,292 +529,300 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="84.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="84.58203125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>32</v>
+      <c r="B3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="2">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B8" s="11" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B13" s="2">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B14" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.25">
-      <c r="B16" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A18" s="9" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2" s="8" customFormat="1" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A24" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A25" s="8" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
-        <v>1.335</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="A27" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B8" r:id="rId1"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="38.7109375" customWidth="1"/>
-    <col min="3" max="3" width="53.85546875" customWidth="1"/>
-    <col min="4" max="4" width="32.28515625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>500</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="4">
-        <v>0.16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6">
-        <f>B4/B2</f>
-        <v>3.2000000000000003E-4</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="8">
-        <f>B6/About!A26</f>
-        <v>2.3970037453183523E-4</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9">
-        <v>2000</v>
-      </c>
-      <c r="C9" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11">
-        <f>B7*B9</f>
-        <v>0.47940074906367047</v>
-      </c>
-      <c r="C11" t="s">
-        <v>31</v>
-      </c>
+    </row>
+    <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B10" s="2"/>
+    </row>
+    <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B11" s="2"/>
+    </row>
+    <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B12" s="2"/>
+    </row>
+    <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B13" s="2"/>
+    </row>
+    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B14" s="2"/>
+    </row>
+    <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B15" s="2"/>
+    </row>
+    <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="2"/>
+    </row>
+    <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="2"/>
+    </row>
+    <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="3"/>
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="3"/>
+      <c r="B21" s="2"/>
+    </row>
+    <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="3"/>
+      <c r="B22" s="2"/>
+    </row>
+    <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="5"/>
+      <c r="B23" s="2"/>
+    </row>
+    <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="3"/>
+      <c r="B24" s="2"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A25" s="4"/>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A26" s="4"/>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A27" s="4"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="25.28515625" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
+    <col min="1" max="1" width="25.25" customWidth="1"/>
+    <col min="2" max="2" width="17.58203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="B1" s="12" t="s">
-        <v>39</v>
+    <row r="1" spans="1:2" ht="34" x14ac:dyDescent="0.45">
+      <c r="B1" s="6" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="B2">
-        <f>Data!B11</f>
-        <v>0.47940074906367047</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4075C59-0419-4623-A6F5-A95F2242D062}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ED3FFE2-F9EE-4493-84EE-3C3F08844AE8}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B89325C-3DA7-41A0-80B2-655C8151EC15}"/>
 </file>
--- a/InputData/trans/EoFoNVFE/Effect of Feebate on New Veh Fuel Econ.xlsx
+++ b/InputData/trans/EoFoNVFE/Effect of Feebate on New Veh Fuel Econ.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iamho\Dropbox\Energy Innovation\InputData_RevisionRequest\trans\EoFoNVFE\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\내 드라이브\2026\01.EPS\01.EI\01.메일_업무협의\260122_메일회신\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D4CC21-B625-4A9E-8630-9FED570EF2A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F46A1401-A5F5-46B1-A3E9-F68876C42051}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13700" yWindow="730" windowWidth="19800" windowHeight="17010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="EoFoNVFE" sheetId="3" r:id="rId2"/>
+    <sheet name="Data" sheetId="2" r:id="rId2"/>
+    <sheet name="EoFoNVFE" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="40">
   <si>
     <t>EoFoNVFE Effect of Feebate on New Veh Fuel Economy</t>
   </si>
@@ -29,33 +43,126 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>Feebates, rebates and gas-guzzler taxes: a study of incentives for increased fuel economy.</t>
+  </si>
+  <si>
+    <t>Energy Policy, 33(6), 757-775.</t>
+  </si>
+  <si>
+    <t>http://cta.ornl.gov/cta/Publications/Reports/FeebateEnergyPolicy_FINAL.pdf</t>
+  </si>
+  <si>
+    <t>Greene, D. L., Patterson, P. D., Singh, M., &amp; Li, J.</t>
+  </si>
+  <si>
+    <t>Feebate Amount</t>
+  </si>
+  <si>
+    <t>per Unit</t>
+  </si>
+  <si>
+    <t>Resulting Increase in Fuel Econ</t>
+  </si>
+  <si>
+    <t>percent</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Feebate Rate</t>
+  </si>
+  <si>
+    <t>hundredth gal/mile (0.01 gal/mile)</t>
+  </si>
+  <si>
+    <t>Page 761, Section 3, Paragrah 1 and Page 771, Section A.2, Paragraph 2</t>
+  </si>
+  <si>
     <t>New Vehicle Fuel Econ</t>
   </si>
   <si>
+    <t>Note:</t>
+  </si>
+  <si>
+    <t>See "cpi.xlsx" in the InputData folder for source information.</t>
+  </si>
+  <si>
+    <t>We adjust 2000 dollars to 2012 dollars using the following conversion factor:</t>
+  </si>
+  <si>
+    <t>The source specifies that it uses 2000 $, for example, Page 762, Table 1A.</t>
+  </si>
+  <si>
+    <t>2000$</t>
+  </si>
+  <si>
+    <t>perc increase in fuel econ / 2000$</t>
+  </si>
+  <si>
+    <t>perc increase in fuel econ / 2012$</t>
+  </si>
+  <si>
+    <t>Since the feebate is natively expressed in unusual units (dollars per (hundredth gallon per mile)), we</t>
+  </si>
+  <si>
+    <t>cause the lever in the EPS to represent the fraction of the best practice feebate rate, to improve</t>
+  </si>
+  <si>
+    <t>Currency Year</t>
+  </si>
+  <si>
+    <t>Best Practice Feebate Rate</t>
+  </si>
+  <si>
+    <t>2012$ / (hundredth gal/mile)</t>
+  </si>
+  <si>
+    <t>Feebate at Full Policy Implementation</t>
+  </si>
+  <si>
+    <t>perc increase in fuel econ at full policy implementation</t>
+  </si>
+  <si>
+    <t>Effect of Feebate on Fuel Economy</t>
+  </si>
+  <si>
+    <t>Best Practices for Feebate Program Design and Implementation</t>
+  </si>
+  <si>
+    <t>http://www.theicct.org/sites/default/files/publications/ICCT_feebates_may2010.pdf</t>
+  </si>
+  <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>John German and Dan Meszler, ICCT</t>
+  </si>
+  <si>
+    <t>This rate is from Germany.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
     <t>Effect of Feebate (dimensionless)</t>
   </si>
   <si>
-    <t>no data</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>Notes</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">In South Korea, there is no subsidies or tax benefits for fuel-efficient vehicles. </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>We set all values to be 0.</t>
-    <phoneticPr fontId="5" type="noConversion"/>
+    <t>model usability for users. As Korea does not currently implement a feebate policy, the same data set is applied.</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +174,14 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -102,12 +217,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="5">
@@ -155,46 +276,58 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
+  <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyProtection="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFont="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyProtection="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyNumberFormat="0" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="7">
-    <cellStyle name="Body: normal cell" xfId="4" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Font: Calibri, 9pt regular" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Footnotes: top row" xfId="6" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Header: bottom row" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="Parent row" xfId="5" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="Table title" xfId="1" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+  <cellStyles count="8">
+    <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Font: Calibri, 9pt regular" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Footnotes: top row" xfId="7" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Header: bottom row" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Parent row" xfId="6" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Table title" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -210,9 +343,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -250,9 +383,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -285,26 +418,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -337,26 +453,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -531,298 +630,281 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B27"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="84.58203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="84.625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1"/>
+      <c r="B5" s="2">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A5" s="5" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="2"/>
-    </row>
-    <row r="11" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B11" s="2"/>
-    </row>
-    <row r="12" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B12" s="2"/>
-    </row>
-    <row r="13" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B13" s="2"/>
-    </row>
-    <row r="14" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B14" s="2"/>
-    </row>
-    <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B15" s="2"/>
-    </row>
-    <row r="16" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B16" s="2"/>
-    </row>
-    <row r="19" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="2"/>
-    </row>
-    <row r="20" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="3"/>
-      <c r="B20" s="2"/>
-    </row>
-    <row r="21" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="3"/>
-      <c r="B21" s="2"/>
-    </row>
-    <row r="22" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="3"/>
-      <c r="B22" s="2"/>
-    </row>
-    <row r="23" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A23" s="5"/>
-      <c r="B23" s="2"/>
-    </row>
-    <row r="24" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A24" s="3"/>
-      <c r="B24" s="2"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A25" s="4"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A26" s="4"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A27" s="4"/>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B11" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>1.335</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="B8" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="38.75" customWidth="1"/>
+    <col min="3" max="3" width="53.875" customWidth="1"/>
+    <col min="4" max="4" width="32.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>500</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>0.16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6">
+        <f>B4/B2</f>
+        <v>3.2000000000000003E-4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <f>B6/About!A26</f>
+        <v>2.3970037453183523E-4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9">
+        <v>2000</v>
+      </c>
+      <c r="C9" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11">
+        <f>B7*B9</f>
+        <v>0.47940074906367047</v>
+      </c>
+      <c r="C11" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.25" customWidth="1"/>
-    <col min="2" max="2" width="17.58203125" customWidth="1"/>
+    <col min="2" max="2" width="17.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="34" x14ac:dyDescent="0.45">
-      <c r="B1" s="6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" ht="33" x14ac:dyDescent="0.3">
+      <c r="B1" s="8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <f>Data!B11</f>
+        <v>0.47940074906367047</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
-    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C4075C59-0419-4623-A6F5-A95F2242D062}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0ED3FFE2-F9EE-4493-84EE-3C3F08844AE8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B89325C-3DA7-41A0-80B2-655C8151EC15}"/>
 </file>